--- a/testxl/Ведомость_отправочных_марок.xlsx
+++ b/testxl/Ведомость_отправочных_марок.xlsx
@@ -1749,7 +1749,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1783,6 +1783,14 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1856,16 +1864,16 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
